--- a/data/use_cases/uc02_goz_min_2556_bep_result.xlsx
+++ b/data/use_cases/uc02_goz_min_2556_bep_result.xlsx
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.247н / группа 3 / уровень 1 / оклад 40400</t>
+          <t>3.247н / группа 3 / уровень 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2663,7 +2663,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Дата построения 03.07.2026</t>
+          <t>Дата построения 10.07.2026</t>
         </is>
       </c>
     </row>
